--- a/Listado codigos lentes medicontur.xlsx
+++ b/Listado codigos lentes medicontur.xlsx
@@ -413,10 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C333"/>
+  <dimension ref="A2:C341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -6058,6 +6057,142 @@
       <c r="C333" t="inlineStr">
         <is>
           <t>BI-FLEX EDOF POB-MA ELON 29.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>A45DT</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -01.0 CYL 3.00 D</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -01.0 CYL 3.00 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>A45DT</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -3.00 CYL 3.00</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -3.00 CYL 3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>A45RD2</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45RD2</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45RD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>A46R</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A46R + 7.00 D</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A46R + 7.00 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>A46R</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A46R + 7.25 D</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A46R + 7.25 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>690MY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>BASIS Z TRIFOCAL 690MY</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>BASIS Z TRIFOCAL 690MY</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>860PAY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>BASIS Z ASPHERIC PRELOADED 860PAY</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BASIS Z ASPHERIC PRELOADED 860PAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>860PEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>BASIS Z EDOF PRELOADED 860PEY</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>BASIS Z EDOF PRELOADED 860PEY</t>
         </is>
       </c>
     </row>
